--- a/WorkBot/refactor/data/orders/Hill & Markes/Hill & Markes_Downtown_2025-10-10.xlsx
+++ b/WorkBot/refactor/data/orders/Hill & Markes/Hill & Markes_Downtown_2025-10-10.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -521,6 +521,33 @@
       <c r="E4" t="inlineStr">
         <is>
           <t>30.94</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>KLP704534</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Trash Bag (33x40)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>25.30</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>25.30</t>
         </is>
       </c>
     </row>
